--- a/बजेट माग estimate/नगर बजेट estimate/लामाटोल सामुदायिक अधुरो भवन/लामाटोल सामुदायिक अधुरो भवन.xlsx
+++ b/बजेट माग estimate/नगर बजेट estimate/लामाटोल सामुदायिक अधुरो भवन/लामाटोल सामुदायिक अधुरो भवन.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{544B8572-3A3D-4BB5-B8B7-8AFE5F85C3C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB29E782-F5AF-495C-9C2F-A7FB883D21D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,8 @@
     <definedName name="description_781">#REF!</definedName>
     <definedName name="description_783">[1]Abstract!$B$301</definedName>
     <definedName name="description_784">[3]Abstract!$B$300</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$66</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$69</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">estimate!$1:$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="61">
   <si>
     <t>Government of Nepal</t>
   </si>
@@ -241,6 +242,9 @@
       </rPr>
       <t xml:space="preserve"> nfdf6f]n ;fd'bflos cw'/f] ejg</t>
     </r>
+  </si>
+  <si>
+    <t>-deduction for footing area</t>
   </si>
 </sst>
 </file>
@@ -540,6 +544,22 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -562,22 +582,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1104,7 +1108,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K66"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" customWidth="1"/>
@@ -1119,113 +1123,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
     </row>
     <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
     </row>
     <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="58"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="59" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
+      <c r="B6" s="59"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="54" t="s">
+      <c r="H6" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="60"/>
+      <c r="K6" s="60"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="48" t="s">
+      <c r="H7" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="48"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="54"/>
+      <c r="K7" s="54"/>
     </row>
     <row r="8" spans="1:11" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
@@ -1788,8 +1792,8 @@
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
       <c r="G28" s="44">
-        <f>SUM(G11:G27)</f>
-        <v>735.22458396830234</v>
+        <f>SUM(G10:G27)</f>
+        <v>859.65006400487664</v>
       </c>
       <c r="H28" s="19" t="s">
         <v>39</v>
@@ -1799,7 +1803,7 @@
       </c>
       <c r="J28" s="44">
         <f>G28*I28</f>
-        <v>134185.83882005487</v>
+        <v>156894.73318153003</v>
       </c>
       <c r="K28" s="18"/>
     </row>
@@ -1817,7 +1821,7 @@
       <c r="I29" s="2"/>
       <c r="J29" s="44">
         <f>0.13*G28*(1871.42/18.94)</f>
-        <v>9443.9714266575957</v>
+        <v>11042.218688563929</v>
       </c>
       <c r="K29" s="18"/>
     </row>
@@ -2037,209 +2041,233 @@
         <v>1</v>
       </c>
       <c r="D41" s="3">
-        <f>44.17/3.281</f>
-        <v>13.462359036879</v>
+        <f>34.25/3.281</f>
+        <v>10.438890582139591</v>
       </c>
       <c r="E41" s="3">
-        <f>36/3.281</f>
-        <v>10.97226455348979</v>
+        <f>20.5/3.281</f>
+        <v>6.2480950929594634</v>
       </c>
       <c r="F41" s="13">
         <v>0.15</v>
       </c>
       <c r="G41" s="3">
-        <f>PRODUCT(C41:F41)</f>
-        <v>22.156884730005061</v>
+        <f t="shared" ref="G41:G43" si="17">PRODUCT(C41:F41)</f>
+        <v>9.7834771533310683</v>
       </c>
       <c r="H41" s="13"/>
       <c r="I41" s="13"/>
       <c r="J41" s="13"/>
       <c r="K41" s="13"/>
     </row>
-    <row r="42" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="15"/>
-      <c r="B42" s="16" t="s">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="13"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="13">
+        <v>1</v>
+      </c>
+      <c r="D42" s="3">
+        <f>21.75/3.281</f>
+        <v>6.6290765010667476</v>
+      </c>
+      <c r="E42" s="3">
+        <f>22.33/3.281</f>
+        <v>6.8058518744285275</v>
+      </c>
+      <c r="F42" s="13">
+        <v>0.15</v>
+      </c>
+      <c r="G42" s="3">
+        <f t="shared" si="17"/>
+        <v>6.767476909577284</v>
+      </c>
+      <c r="H42" s="13"/>
+      <c r="I42" s="13"/>
+      <c r="J42" s="13"/>
+      <c r="K42" s="13"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="13"/>
+      <c r="B43" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C43" s="13">
+        <v>-4</v>
+      </c>
+      <c r="D43" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="F43" s="13">
+        <v>0.15</v>
+      </c>
+      <c r="G43" s="3">
+        <f t="shared" si="17"/>
+        <v>-0.216</v>
+      </c>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
+      <c r="J43" s="13"/>
+      <c r="K43" s="13"/>
+    </row>
+    <row r="44" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="15"/>
+      <c r="B44" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="17"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="18"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="2">
-        <f>SUM(G41)</f>
-        <v>22.156884730005061</v>
-      </c>
-      <c r="H42" s="19" t="s">
+      <c r="C44" s="17"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="2">
+        <f>SUM(G41:G43)</f>
+        <v>16.334954062908352</v>
+      </c>
+      <c r="H44" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="I42" s="2">
+      <c r="I44" s="2">
         <v>4495.6400000000003</v>
       </c>
-      <c r="J42" s="60">
-        <f>G42*I42</f>
-        <v>99609.377267599964</v>
-      </c>
-      <c r="K42" s="18"/>
-    </row>
-    <row r="43" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="21"/>
-      <c r="B43" s="22" t="s">
+      <c r="J44" s="47">
+        <f>G44*I44</f>
+        <v>73436.072883373316</v>
+      </c>
+      <c r="K44" s="18"/>
+    </row>
+    <row r="45" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="21"/>
+      <c r="B45" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="C43" s="23"/>
-      <c r="D43" s="24"/>
-      <c r="E43" s="24"/>
-      <c r="F43" s="24"/>
-      <c r="G43" s="24"/>
-      <c r="H43" s="23"/>
-      <c r="I43" s="23"/>
-      <c r="J43" s="20">
-        <f>0.13*G42*3093.15</f>
-        <v>8909.4938403399701</v>
-      </c>
-      <c r="K43" s="23"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="13"/>
-      <c r="B44" s="13"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="13"/>
-      <c r="H44" s="13"/>
-      <c r="I44" s="13"/>
-      <c r="J44" s="13"/>
-      <c r="K44" s="13"/>
-    </row>
-    <row r="45" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A45" s="11">
-        <v>4</v>
-      </c>
-      <c r="B45" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="C45" s="13"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
-      <c r="I45" s="13"/>
-      <c r="J45" s="13"/>
-      <c r="K45" s="13"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="24"/>
+      <c r="E45" s="24"/>
+      <c r="F45" s="24"/>
+      <c r="G45" s="24"/>
+      <c r="H45" s="23"/>
+      <c r="I45" s="23"/>
+      <c r="J45" s="20">
+        <f>0.13*G44*3093.15</f>
+        <v>6568.4402107590467</v>
+      </c>
+      <c r="K45" s="23"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="13"/>
-      <c r="B46" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C46" s="13">
-        <v>1</v>
-      </c>
-      <c r="D46" s="3">
-        <f>44.17/3.281</f>
-        <v>13.462359036879</v>
-      </c>
-      <c r="E46" s="3">
-        <f>36/3.281</f>
-        <v>10.97226455348979</v>
-      </c>
-      <c r="F46" s="13">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G46" s="3">
-        <f>PRODUCT(C46:F46)</f>
-        <v>11.07844236500253</v>
-      </c>
+      <c r="B46" s="13"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
       <c r="H46" s="13"/>
       <c r="I46" s="13"/>
       <c r="J46" s="13"/>
       <c r="K46" s="13"/>
     </row>
-    <row r="47" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="15"/>
-      <c r="B47" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" s="17"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="18"/>
-      <c r="F47" s="18"/>
-      <c r="G47" s="2">
-        <f>SUM(G46)</f>
-        <v>11.07844236500253</v>
-      </c>
-      <c r="H47" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="I47" s="2">
-        <v>12884.61</v>
-      </c>
-      <c r="J47" s="60">
-        <f>G47*I47</f>
-        <v>142741.40928053527</v>
-      </c>
-      <c r="K47" s="18"/>
-    </row>
-    <row r="48" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="21"/>
-      <c r="B48" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="C48" s="23"/>
-      <c r="D48" s="24"/>
-      <c r="E48" s="24"/>
-      <c r="F48" s="24"/>
-      <c r="G48" s="24"/>
-      <c r="H48" s="23"/>
-      <c r="I48" s="23"/>
-      <c r="J48" s="20">
-        <f>0.13*G47*4169.92</f>
-        <v>6005.5083902672759</v>
-      </c>
-      <c r="K48" s="23"/>
+    <row r="47" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A47" s="11">
+        <v>4</v>
+      </c>
+      <c r="B47" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="C47" s="13"/>
+      <c r="D47" s="13"/>
+      <c r="E47" s="13"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="13"/>
+      <c r="H47" s="13"/>
+      <c r="I47" s="13"/>
+      <c r="J47" s="13"/>
+      <c r="K47" s="13"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="13"/>
+      <c r="B48" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C48" s="13">
+        <v>1</v>
+      </c>
+      <c r="D48" s="3">
+        <f>D41</f>
+        <v>10.438890582139591</v>
+      </c>
+      <c r="E48" s="3">
+        <f>E41</f>
+        <v>6.2480950929594634</v>
+      </c>
+      <c r="F48" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="G48" s="3">
+        <f t="shared" ref="G48:G49" si="18">PRODUCT(C48:F48)</f>
+        <v>6.5223181022207131</v>
+      </c>
+      <c r="H48" s="13"/>
+      <c r="I48" s="13"/>
+      <c r="J48" s="13"/>
+      <c r="K48" s="13"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="13"/>
-      <c r="B49" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C49" s="23"/>
-      <c r="D49" s="24"/>
-      <c r="E49" s="24"/>
-      <c r="F49" s="24"/>
-      <c r="G49" s="24"/>
-      <c r="H49" s="23"/>
-      <c r="I49" s="23"/>
-      <c r="J49" s="20">
-        <f>0.13*G47*1414.16</f>
-        <v>2036.6697071359574</v>
-      </c>
+      <c r="B49" s="14"/>
+      <c r="C49" s="13">
+        <v>1</v>
+      </c>
+      <c r="D49" s="3">
+        <f>D42</f>
+        <v>6.6290765010667476</v>
+      </c>
+      <c r="E49" s="3">
+        <f>E42</f>
+        <v>6.8058518744285275</v>
+      </c>
+      <c r="F49" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="G49" s="3">
+        <f t="shared" si="18"/>
+        <v>4.5116512730515224</v>
+      </c>
+      <c r="H49" s="13"/>
+      <c r="I49" s="13"/>
+      <c r="J49" s="13"/>
       <c r="K49" s="13"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" s="13"/>
-      <c r="B50" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="C50" s="23"/>
-      <c r="D50" s="24"/>
-      <c r="E50" s="24"/>
-      <c r="F50" s="24"/>
-      <c r="G50" s="24"/>
-      <c r="H50" s="23"/>
-      <c r="I50" s="23"/>
-      <c r="J50" s="20">
-        <f>0.13*G47*(1652.5+1106.96)</f>
-        <v>3974.167413908885</v>
-      </c>
-      <c r="K50" s="13"/>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" s="13"/>
+    <row r="50" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="15"/>
+      <c r="B50" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" s="17"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="2">
+        <f>SUM(G48:G49)</f>
+        <v>11.033969375272235</v>
+      </c>
+      <c r="H50" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="I50" s="2">
+        <v>12884.61</v>
+      </c>
+      <c r="J50" s="47">
+        <f>G50*I50</f>
+        <v>142168.39215232641</v>
+      </c>
+      <c r="K50" s="18"/>
+    </row>
+    <row r="51" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="21"/>
       <c r="B51" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C51" s="23"/>
       <c r="D51" s="24"/>
@@ -2249,15 +2277,15 @@
       <c r="H51" s="23"/>
       <c r="I51" s="23"/>
       <c r="J51" s="20">
-        <f>0.13*G47*36.4</f>
-        <v>52.423189271191973</v>
-      </c>
-      <c r="K51" s="13"/>
+        <f>0.13*G50*4169.92</f>
+        <v>5981.4000450535768</v>
+      </c>
+      <c r="K51" s="23"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="13"/>
       <c r="B52" s="22" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="C52" s="23"/>
       <c r="D52" s="24"/>
@@ -2267,8 +2295,8 @@
       <c r="H52" s="23"/>
       <c r="I52" s="23"/>
       <c r="J52" s="20">
-        <f>0.13*G47*392.92</f>
-        <v>565.88240462738327</v>
+        <f>0.13*G50*1414.16</f>
+        <v>2028.4937571255482</v>
       </c>
       <c r="K52" s="13"/>
     </row>
@@ -2285,219 +2313,269 @@
       <c r="H53" s="23"/>
       <c r="I53" s="23"/>
       <c r="J53" s="20">
-        <f>0.13*G47*14.15</f>
-        <v>20.378794730422157</v>
+        <f>0.13*G50*(1652.5+1106.96)</f>
+        <v>3958.2136271975342</v>
       </c>
       <c r="K53" s="13"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="13"/>
-      <c r="B54" s="13"/>
-      <c r="C54" s="13"/>
-      <c r="D54" s="13"/>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="13"/>
-      <c r="H54" s="13"/>
-      <c r="I54" s="13"/>
-      <c r="J54" s="13"/>
+      <c r="B54" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C54" s="23"/>
+      <c r="D54" s="24"/>
+      <c r="E54" s="24"/>
+      <c r="F54" s="24"/>
+      <c r="G54" s="24"/>
+      <c r="H54" s="23"/>
+      <c r="I54" s="23"/>
+      <c r="J54" s="20">
+        <f>0.13*G50*36.4</f>
+        <v>52.212743083788219</v>
+      </c>
       <c r="K54" s="13"/>
     </row>
-    <row r="55" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="15">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" s="13"/>
+      <c r="B55" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C55" s="23"/>
+      <c r="D55" s="24"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="24"/>
+      <c r="G55" s="24"/>
+      <c r="H55" s="23"/>
+      <c r="I55" s="23"/>
+      <c r="J55" s="20">
+        <f>0.13*G50*392.92</f>
+        <v>563.61074210115578</v>
+      </c>
+      <c r="K55" s="13"/>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" s="13"/>
+      <c r="B56" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="23"/>
+      <c r="D56" s="24"/>
+      <c r="E56" s="24"/>
+      <c r="F56" s="24"/>
+      <c r="G56" s="24"/>
+      <c r="H56" s="23"/>
+      <c r="I56" s="23"/>
+      <c r="J56" s="20">
+        <f>0.13*G50*14.15</f>
+        <v>20.296986665813279</v>
+      </c>
+      <c r="K56" s="13"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" s="13"/>
+      <c r="B57" s="13"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="K57" s="13"/>
+    </row>
+    <row r="58" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="15">
         <v>5</v>
       </c>
-      <c r="B55" s="26" t="s">
+      <c r="B58" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C55" s="17">
+      <c r="C58" s="17">
         <v>1</v>
       </c>
-      <c r="D55" s="1"/>
-      <c r="E55" s="18"/>
-      <c r="F55" s="18"/>
-      <c r="G55" s="19">
-        <f t="shared" ref="G55" si="17">PRODUCT(C55:F55)</f>
-        <v>1</v>
-      </c>
-      <c r="H55" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="I55" s="2">
-        <v>7000</v>
-      </c>
-      <c r="J55" s="19">
-        <f>G55*I55</f>
-        <v>7000</v>
-      </c>
-      <c r="K55" s="18"/>
-    </row>
-    <row r="56" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="15"/>
-      <c r="B56" s="27"/>
-      <c r="C56" s="17"/>
-      <c r="D56" s="1"/>
-      <c r="E56" s="18"/>
-      <c r="F56" s="18"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="19"/>
-      <c r="I56" s="2"/>
-      <c r="J56" s="20"/>
-      <c r="K56" s="18"/>
-    </row>
-    <row r="57" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="15">
-        <v>6</v>
-      </c>
-      <c r="B57" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="C57" s="17">
-        <v>1</v>
-      </c>
-      <c r="D57" s="1"/>
-      <c r="E57" s="18"/>
-      <c r="F57" s="18"/>
-      <c r="G57" s="19">
-        <f t="shared" ref="G57" si="18">PRODUCT(C57:F57)</f>
-        <v>1</v>
-      </c>
-      <c r="H57" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="I57" s="2">
-        <v>500</v>
-      </c>
-      <c r="J57" s="19">
-        <f>G57*I57</f>
-        <v>500</v>
-      </c>
-      <c r="K57" s="18"/>
-    </row>
-    <row r="58" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="15"/>
-      <c r="B58" s="27"/>
-      <c r="C58" s="17"/>
       <c r="D58" s="1"/>
       <c r="E58" s="18"/>
       <c r="F58" s="18"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="19"/>
-      <c r="I58" s="2"/>
-      <c r="J58" s="20"/>
+      <c r="G58" s="19">
+        <f t="shared" ref="G58" si="19">PRODUCT(C58:F58)</f>
+        <v>1</v>
+      </c>
+      <c r="H58" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="I58" s="2">
+        <v>7500</v>
+      </c>
+      <c r="J58" s="19">
+        <f>G58*I58</f>
+        <v>7500</v>
+      </c>
       <c r="K58" s="18"/>
     </row>
     <row r="59" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="28"/>
-      <c r="B59" s="29" t="s">
+      <c r="A59" s="15"/>
+      <c r="B59" s="27"/>
+      <c r="C59" s="17"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="18"/>
+      <c r="F59" s="18"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="19"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="20">
+        <v>0</v>
+      </c>
+      <c r="K59" s="18"/>
+    </row>
+    <row r="60" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="15">
+        <v>6</v>
+      </c>
+      <c r="B60" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C60" s="17">
+        <v>1</v>
+      </c>
+      <c r="D60" s="1"/>
+      <c r="E60" s="18"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="19">
+        <f t="shared" ref="G60" si="20">PRODUCT(C60:F60)</f>
+        <v>1</v>
+      </c>
+      <c r="H60" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="I60" s="2">
+        <v>500</v>
+      </c>
+      <c r="J60" s="19">
+        <f>G60*I60</f>
+        <v>500</v>
+      </c>
+      <c r="K60" s="18"/>
+    </row>
+    <row r="61" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="15"/>
+      <c r="B61" s="27"/>
+      <c r="C61" s="17"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="18"/>
+      <c r="F61" s="18"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="20"/>
+      <c r="K61" s="18"/>
+    </row>
+    <row r="62" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="28"/>
+      <c r="B62" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="C59" s="30"/>
-      <c r="D59" s="31"/>
-      <c r="E59" s="31"/>
-      <c r="F59" s="31"/>
-      <c r="G59" s="20"/>
-      <c r="H59" s="20"/>
-      <c r="I59" s="20"/>
-      <c r="J59" s="20">
-        <f>SUM(J10:J57)</f>
-        <v>597058.1174791028</v>
-      </c>
-      <c r="K59" s="32"/>
-    </row>
-    <row r="60" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="1:11" s="40" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="33"/>
-      <c r="B61" s="34" t="s">
+      <c r="C62" s="30"/>
+      <c r="D62" s="31"/>
+      <c r="E62" s="31"/>
+      <c r="F62" s="31"/>
+      <c r="G62" s="20"/>
+      <c r="H62" s="20"/>
+      <c r="I62" s="20"/>
+      <c r="J62" s="20">
+        <f>SUM(J10:J60)</f>
+        <v>592727.08196175424</v>
+      </c>
+      <c r="K62" s="32"/>
+    </row>
+    <row r="63" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:11" s="40" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="33"/>
+      <c r="B64" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="C61" s="55">
-        <f>J59</f>
-        <v>597058.1174791028</v>
-      </c>
-      <c r="D61" s="56"/>
-      <c r="E61" s="35">
+      <c r="C64" s="48">
+        <f>J62</f>
+        <v>592727.08196175424</v>
+      </c>
+      <c r="D64" s="49"/>
+      <c r="E64" s="35">
         <v>100</v>
       </c>
-      <c r="F61" s="33"/>
-      <c r="G61" s="36"/>
-      <c r="H61" s="33"/>
-      <c r="I61" s="37"/>
-      <c r="J61" s="38"/>
-      <c r="K61" s="39"/>
-    </row>
-    <row r="62" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="C62" s="57">
-        <v>500000</v>
-      </c>
-      <c r="D62" s="58"/>
-      <c r="E62" s="35"/>
-    </row>
-    <row r="63" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="C63" s="57">
-        <f>C62-C65-C66</f>
-        <v>475000</v>
-      </c>
-      <c r="D63" s="58"/>
-      <c r="E63" s="35">
-        <f>C63/C61*100</f>
-        <v>79.556744325919851</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="C64" s="59">
-        <f>C61-C63</f>
-        <v>122058.1174791028</v>
-      </c>
-      <c r="D64" s="59"/>
-      <c r="E64" s="35">
-        <f>100-E63</f>
-        <v>20.443255674080149</v>
-      </c>
+      <c r="F64" s="33"/>
+      <c r="G64" s="36"/>
+      <c r="H64" s="33"/>
+      <c r="I64" s="37"/>
+      <c r="J64" s="38"/>
+      <c r="K64" s="39"/>
     </row>
     <row r="65" spans="2:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B65" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="C65" s="55">
-        <f>C62*0.03</f>
-        <v>15000</v>
-      </c>
-      <c r="D65" s="56"/>
-      <c r="E65" s="35">
-        <v>3</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="C65" s="50">
+        <v>500000</v>
+      </c>
+      <c r="D65" s="51"/>
+      <c r="E65" s="35"/>
     </row>
     <row r="66" spans="2:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B66" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="C66" s="50">
+        <f>C65-C68-C69</f>
+        <v>475000</v>
+      </c>
+      <c r="D66" s="51"/>
+      <c r="E66" s="35">
+        <f>C66/C64*100</f>
+        <v>80.138062601743826</v>
+      </c>
+    </row>
+    <row r="67" spans="2:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="C67" s="52">
+        <f>C64-C66</f>
+        <v>117727.08196175424</v>
+      </c>
+      <c r="D67" s="52"/>
+      <c r="E67" s="35">
+        <f>100-E66</f>
+        <v>19.861937398256174</v>
+      </c>
+    </row>
+    <row r="68" spans="2:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="C68" s="48">
+        <f>C65*0.03</f>
+        <v>15000</v>
+      </c>
+      <c r="D68" s="49"/>
+      <c r="E68" s="35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="2:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="C66" s="55">
-        <f>C62*0.02</f>
+      <c r="C69" s="48">
+        <f>C65*0.02</f>
         <v>10000</v>
       </c>
-      <c r="D66" s="56"/>
-      <c r="E66" s="35">
+      <c r="D69" s="49"/>
+      <c r="E69" s="35">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C65:D65"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="H7:K7"/>
     <mergeCell ref="A1:K1"/>
@@ -2507,8 +2585,20 @@
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C68:D68"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;LPrepared By:&amp;CChecked By:&amp;RApproved By:</oddFooter>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="41" max="10" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>